--- a/docs/_baseline/mammal_bulk.xlsx
+++ b/docs/_baseline/mammal_bulk.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148">
   <si>
     <t>※ 엑셀 기반 수질/생태계 데이터 베이스 작성/관리 시 주의 사항</t>
   </si>
@@ -126,6 +126,9 @@
     <t>너구리</t>
   </si>
   <si>
+    <t>멧토끼</t>
+  </si>
+  <si>
     <t>두더지</t>
   </si>
   <si>
@@ -139,6 +142,9 @@
   </si>
   <si>
     <t>Nyctereutes procyonoides</t>
+  </si>
+  <si>
+    <t>Lepus coreanus</t>
   </si>
   <si>
     <t>Mogera robusta</t>
@@ -1488,7 +1494,7 @@
       <c r="H1" s="32"/>
       <c r="I1" s="12"/>
       <c r="J1" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
@@ -1499,10 +1505,10 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="44"/>
       <c r="S1" s="48" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T1" s="53" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U1" s="56"/>
       <c r="V1" s="56"/>
@@ -1516,10 +1522,10 @@
       <c r="AD1" s="56"/>
       <c r="AE1" s="60"/>
       <c r="AF1" s="63" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AG1" s="63" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="21" s="70" customFormat="true" customHeight="true">
@@ -1545,33 +1551,33 @@
         <v>32</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" s="36" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K2" s="34"/>
       <c r="L2" s="34"/>
       <c r="M2" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N2" s="34"/>
       <c r="O2" s="34"/>
       <c r="P2" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R2" s="45"/>
       <c r="S2" s="49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T2" s="54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U2" s="57"/>
       <c r="V2" s="57"/>
@@ -1585,10 +1591,10 @@
       <c r="AD2" s="57"/>
       <c r="AE2" s="61"/>
       <c r="AF2" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AG2" s="68" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="53.25" s="70" customFormat="true" customHeight="true">
@@ -1611,71 +1617,71 @@
       <c r="G3" s="28"/>
       <c r="H3" s="34"/>
       <c r="I3" s="36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J3" s="40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L3" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="19" t="s">
-        <v>48</v>
-      </c>
       <c r="N3" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="42"/>
       <c r="R3" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S3" s="50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T3" s="55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U3" s="58" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="V3" s="58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="W3" s="58" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X3" s="58" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y3" s="58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z3" s="58" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA3" s="58" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB3" s="58" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AC3" s="58" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AD3" s="59" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AE3" s="62" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AF3" s="65"/>
       <c r="AG3" s="65"/>
@@ -1703,10 +1709,10 @@
         <v>33</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J4" s="29" t="n">
         <v>37</v>
@@ -1734,7 +1740,7 @@
       </c>
       <c r="R4" s="45"/>
       <c r="S4" s="51" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="T4" s="29"/>
       <c r="U4" s="20"/>
@@ -1749,10 +1755,10 @@
       <c r="AD4" s="20"/>
       <c r="AE4" s="37"/>
       <c r="AF4" s="66" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AG4" s="66" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -1775,10 +1781,10 @@
         <v>34</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J5" s="30"/>
       <c r="K5" s="21"/>
@@ -1794,7 +1800,7 @@
       </c>
       <c r="R5" s="41"/>
       <c r="S5" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T5" s="30" t="n">
         <v>2</v>
@@ -1815,10 +1821,10 @@
       <c r="AD5" s="21"/>
       <c r="AE5" s="38"/>
       <c r="AF5" s="67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AG5" s="67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -1841,10 +1847,10 @@
         <v>35</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J6" s="30"/>
       <c r="K6" s="21"/>
@@ -1860,7 +1866,7 @@
       </c>
       <c r="R6" s="41"/>
       <c r="S6" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T6" s="30" t="n">
         <v>1</v>
@@ -1879,10 +1885,10 @@
       <c r="AD6" s="21"/>
       <c r="AE6" s="38"/>
       <c r="AF6" s="67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AG6" s="67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -1905,10 +1911,10 @@
         <v>33</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J7" s="30"/>
       <c r="K7" s="21"/>
@@ -1924,7 +1930,7 @@
       </c>
       <c r="R7" s="41"/>
       <c r="S7" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T7" s="30"/>
       <c r="U7" s="21" t="n">
@@ -1943,10 +1949,10 @@
       <c r="AD7" s="21"/>
       <c r="AE7" s="38"/>
       <c r="AF7" s="67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AG7" s="67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -1969,10 +1975,10 @@
         <v>36</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="21"/>
@@ -1988,12 +1994,14 @@
       </c>
       <c r="R8" s="41"/>
       <c r="S8" s="41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T8" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="21" t="n">
+        <v>0</v>
+      </c>
       <c r="V8" s="21"/>
       <c r="W8" s="21"/>
       <c r="X8" s="21"/>
@@ -2005,32 +2013,56 @@
       <c r="AD8" s="21"/>
       <c r="AE8" s="38"/>
       <c r="AF8" s="67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AG8" s="67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="16"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="38"/>
+      <c r="B9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>20260514</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>47</v>
+      </c>
       <c r="J9" s="30"/>
       <c r="K9" s="21"/>
       <c r="L9" s="21"/>
       <c r="M9" s="21"/>
       <c r="N9" s="21"/>
       <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="26"/>
+      <c r="P9" s="21" t="n">
+        <v>36.763081</v>
+      </c>
+      <c r="Q9" s="26" t="n">
+        <v>127.090606</v>
+      </c>
       <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="30"/>
+      <c r="S9" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="T9" s="30" t="n">
+        <v>4</v>
+      </c>
       <c r="U9" s="21"/>
       <c r="V9" s="21"/>
       <c r="W9" s="21"/>
@@ -2042,8 +2074,12 @@
       <c r="AC9" s="21"/>
       <c r="AD9" s="21"/>
       <c r="AE9" s="38"/>
-      <c r="AF9" s="67"/>
-      <c r="AG9" s="67"/>
+      <c r="AF9" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG9" s="67" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="16"/>
@@ -5929,7 +5965,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="true">
       <c r="A1" s="74" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -5950,7 +5986,7 @@
     </row>
     <row r="60">
       <c r="U60" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5975,95 +6011,95 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
@@ -6071,13 +6107,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
@@ -6085,13 +6121,13 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -6099,13 +6135,13 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -6113,13 +6149,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22">
@@ -6127,13 +6163,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
@@ -6141,13 +6177,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
@@ -6155,10 +6191,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
@@ -6166,142 +6202,142 @@
         <v>8</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
